--- a/templates/strategy-worksheets.xlsx
+++ b/templates/strategy-worksheets.xlsx
@@ -468,7 +468,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -672,6 +672,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -679,7 +680,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -804,6 +805,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -811,7 +813,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -905,6 +907,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -912,7 +915,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1060,5 +1063,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/templates/strategy-worksheets.xlsx
+++ b/templates/strategy-worksheets.xlsx
@@ -7,10 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Option Scorecard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWOT" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hypothesis Test" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanced Scorecard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWOT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanced Scorecard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +42,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,17 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4CC"/>
+        <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDDDDD"/>
+        <fgColor rgb="00FFF4CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,18 +86,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,219 +457,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Option Scorecard</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Yellow cells are inputs. Blue cells calculate. Replace the example numbers with your own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Rate each option 1 to 5 on each lens. Weights must add to 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Fit</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Traction</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Legal and regulatory</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cost and terms</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Weights total</t>
-        </is>
-      </c>
-      <c r="B11" s="6">
-        <f>SUM(B7:B10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Fit</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Traction</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Legal and regulatory</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Cost and terms</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Weighted total</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6">
-        <f>B14*$B$7+C14*$B$8+D14*$B$9+E14*$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6">
-        <f>B15*$B$7+C15*$B$8+D15*$B$9+E15*$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="6">
-        <f>B16*$B$7+C16*$B$8+D16*$B$9+E16*$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>A legal score of 1 can rule an option out whatever its total.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -712,210 +489,107 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Strengths</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Weaknesses</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Opportunities</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Threats</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr"/>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr"/>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Pairing (S+O or W+T)</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Option it creates</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Next action</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr"/>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr"/>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="9" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hypothesis Test</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Yellow cells are inputs. Blue cells calculate. Replace the example numbers with your own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Write the bet, then the conditions that must all be true.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The bet (Doing X is the best way to achieve Y)</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Condition that must be true</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Data that would prove or disprove it</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Holds? (yes/no)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr"/>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr"/>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="9" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Decision rule: all hold = go, one fails = pivot, several fail = stop</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -947,122 +621,121 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Financial</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Internal process</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="9" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Internal process</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr"/>
-      <c r="C12" s="9" t="inlineStr"/>
-      <c r="D12" s="9" t="inlineStr"/>
-      <c r="E12" s="9" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Learning and growth</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr"/>
-      <c r="D13" s="9" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Learning and growth</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="9" t="inlineStr"/>
-      <c r="D14" s="9" t="inlineStr"/>
-      <c r="E14" s="9" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>